--- a/reconciliation-contenu-teleexpertise/ig/StructureDefinition-cfl-Organization.xlsx
+++ b/reconciliation-contenu-teleexpertise/ig/StructureDefinition-cfl-Organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:58:57+00:00</t>
+    <t>2026-07-24T15:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2416,7 +2416,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/teleexpertise-confluence/StructureDefinition/AsAddressExtendedProfile|0.1.0}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.1.0}
 </t>
   </si>
   <si>
